--- a/examples/wangetal2018/out/ResultFiles/AC_1.0_nfc.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_1.0_nfc.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="379">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>nfc</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,27 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
+    <t>b</t>
   </si>
   <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,28 +133,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>nfc</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -144,6 +178,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -180,6 +217,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -192,6 +235,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -201,27 +247,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -234,39 +301,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -282,6 +340,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -342,12 +403,6 @@
     <t>C_0_2</t>
   </si>
   <si>
-    <t>C_0_3</t>
-  </si>
-  <si>
-    <t>C_0_4</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
@@ -372,15 +427,6 @@
     <t>C_1_6</t>
   </si>
   <si>
-    <t>C_1_7</t>
-  </si>
-  <si>
-    <t>C_1_8</t>
-  </si>
-  <si>
-    <t>C_1_9</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -453,348 +499,303 @@
     <t>Erosional velocity (m/s)</t>
   </si>
   <si>
-    <t>PI01_0_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>PI01_0_remaining</t>
-  </si>
-  <si>
-    <t>PI01_1_pre_C_0_1</t>
+    <t>PI01_0</t>
+  </si>
+  <si>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>PI01_1_pre_C_0_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_0</t>
   </si>
   <si>
     <t>PI01_1_remaining</t>
   </si>
   <si>
-    <t>PI01_pre_C_0_2</t>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N01_1</t>
+  </si>
+  <si>
+    <t>PI01_pre_C_0_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_1</t>
   </si>
   <si>
     <t>PI01_remaining</t>
   </si>
   <si>
-    <t>PI02_0_pre_C_0_3</t>
+    <t>N_post_C_0_1</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
+    <t>PI02_0_pre_C_0_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_2</t>
   </si>
   <si>
     <t>PI02_0_remaining</t>
   </si>
   <si>
-    <t>PI02_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>PI02_remaining</t>
-  </si>
-  <si>
-    <t>PI03_0_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI03_0_remaining</t>
-  </si>
-  <si>
-    <t>PI03_pre_C_1_1</t>
+    <t>N_post_C_0_2</t>
+  </si>
+  <si>
+    <t>N02_0</t>
+  </si>
+  <si>
+    <t>PI02</t>
+  </si>
+  <si>
+    <t>N03</t>
+  </si>
+  <si>
+    <t>PI03_0</t>
+  </si>
+  <si>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
+    <t>PI03_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
   </si>
   <si>
     <t>PI03_remaining</t>
   </si>
   <si>
-    <t>PI04_0_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>PI04_0_pre_C_1_3</t>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0_pre_C_1_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_1</t>
   </si>
   <si>
     <t>PI04_0_remaining</t>
   </si>
   <si>
-    <t>PI04_1_pre_C_1_4</t>
+    <t>N_post_C_1_1</t>
+  </si>
+  <si>
+    <t>N04_0</t>
+  </si>
+  <si>
+    <t>PI04_1_pre_C_1_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_2</t>
   </si>
   <si>
     <t>PI04_1_remaining</t>
   </si>
   <si>
-    <t>PI04_pre_C_1_5</t>
+    <t>N_post_C_1_2</t>
+  </si>
+  <si>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_3</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_3</t>
   </si>
   <si>
     <t>PI04_remaining</t>
   </si>
   <si>
-    <t>PI05_0_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>PI05_0_pre_C_1_7</t>
+    <t>N_post_C_1_3</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>PI05_0_pre_C_1_4</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_4</t>
   </si>
   <si>
     <t>PI05_0_remaining</t>
   </si>
   <si>
-    <t>PI05_1_pre_C_1_8</t>
+    <t>N_post_C_1_4</t>
+  </si>
+  <si>
+    <t>N05_0</t>
+  </si>
+  <si>
+    <t>PI05_1_pre_C_1_5</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_5</t>
   </si>
   <si>
     <t>PI05_1_remaining</t>
   </si>
   <si>
-    <t>PI05_pre_C_1_9</t>
+    <t>N_post_C_1_5</t>
+  </si>
+  <si>
+    <t>N05_1</t>
+  </si>
+  <si>
+    <t>PI05_pre_C_1_6</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_6</t>
   </si>
   <si>
     <t>PI05_remaining</t>
   </si>
   <si>
+    <t>N_post_C_1_6</t>
+  </si>
+  <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1_pre_C_2_0</t>
   </si>
   <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
     <t>PI06_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_2_0</t>
+  </si>
+  <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N_pre_C_2_1</t>
+  </si>
+  <si>
     <t>PI07_0_remaining</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1_pre_C_2_2</t>
   </si>
   <si>
+    <t>N_pre_C_2_2</t>
+  </si>
+  <si>
     <t>PI07_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_2_2</t>
+  </si>
+  <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1_pre_C_3_0</t>
   </si>
   <si>
+    <t>N_pre_C_3_0</t>
+  </si>
+  <si>
     <t>PI08_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_3_0</t>
+  </si>
+  <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N_pre_C_3_1</t>
+  </si>
+  <si>
     <t>PI09_0_remaining</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1_pre_C_3_2</t>
   </si>
   <si>
+    <t>N_pre_C_3_2</t>
+  </si>
+  <si>
     <t>PI09_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_3_2</t>
+  </si>
+  <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_1</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N_post_C_0_2</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N_post_C_0_3</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_4</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N_post_C_1_2</t>
-  </si>
-  <si>
-    <t>N_post_C_1_3</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_4</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_5</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N_post_C_1_6</t>
-  </si>
-  <si>
-    <t>N_post_C_1_7</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_8</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_9</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_1</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N_post_C_2_2</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_3_1</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N_post_C_3_2</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_4</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_3</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_4</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_5</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_6</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_7</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_8</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_9</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_0</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N_pre_C_2_2</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_0</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
-    <t>N_pre_C_3_2</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -862,22 +863,316 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>335309001.82830477</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(65.4655149438955), '2049': np.float64(67.10215281749288), '2050': np.float64(68.77970663793019), '2051': np.float64(70.49919930387846), '2052': np.float64(72.2616792864754), '2053': np.float64(74.06822126863727), '2054': np.float64(75.9199268003532), '2055': np.float64(77.81792497036201), '2056': np.float64(79.76337309462106), '2057': np.float64(81.75745742198659), '2058': np.float64(83.80139385753625), '2059': np.float64(85.89642870397464), '2060': np.float64(88.04383942157399), '2061': np.float64(90.24493540711335), '2062': np.float64(92.50105879229116), '2063': np.float64(94.81358526209844), '2064': np.float64(97.1839248936509), '2065': np.float64(99.61352301599216), '2066': np.float64(102.10386109139195), '2067': np.float64(104.65645761867674), '2068': np.float64(107.27286905914366), '2069': np.float64(109.95469078562223), '2070': np.float64(112.70355805526277), '2071': np.float64(115.52114700664434), '2072': np.float64(118.40917568181044), '2073': np.float64(121.36940507385569), '2074': np.float64(124.40364020070207), '2075': np.float64(127.51373120571961), '2076': np.float64(130.7015744858626), '2077': np.float64(133.96911384800913), '2078': np.float64(137.31834169420938), '2079': np.float64(140.75130023656456), '2080': np.float64(144.27008274247868), '2081': np.float64(147.87683481104065), '2082': np.float64(151.57375568131664), '2020': np.float64(32.790222028526316), '2021': np.float64(33.60997757923947), '2022': np.float64(34.450227018720454), '2023': np.float64(35.31148269418846), '2024': np.float64(36.19426976154317), '2025': np.float64(37.099126505581744), '2026': np.float64(38.02660466822129), '2027': np.float64(38.97726978492682), '2028': np.float64(39.95170152954998), '2029': np.float64(40.95049406778873), '2030': np.float64(41.97425641948344), '2031': np.float64(43.023612829970524), '2032': np.float64(44.09920315071979), '2033': np.float64(45.20168322948777), '2034': np.float64(46.33172531022497), '2035': np.float64(47.490018442980585), '2036': np.float64(48.6772689040551), '2037': np.float64(49.89420062665647), '2038': np.float64(51.14155564232288), '2039': np.float64(52.42009453338094), '2040': np.float64(53.73059689671546), '2041': np.float64(55.07386181913335), '2042': np.float64(56.45070836461168), '2043': np.float64(57.861976073726964), '2044': np.float64(59.30852547557013), '2045': np.float64(60.79123861245938), '2046': np.float64(62.31101957777086), '2047': np.float64(63.868795067215125)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.07554251137707893</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333334</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -893,7 +1188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -901,32 +1196,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1240,14 +1517,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1256,28 +1533,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1285,7 +1562,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1293,7 +1570,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1301,15 +1578,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1317,7 +1594,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1325,7 +1602,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1333,7 +1610,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1341,7 +1618,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1349,63 +1626,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>29</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1413,39 +1690,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1455,268 +1793,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
+      <c r="C1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>3.031968251816166</v>
+        <v>2.934746094080351</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>0.2716576612210982</v>
+        <v>0.2474617271350765</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>0.03706561774991999</v>
+        <v>0.03745263840848296</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>0.007659366812753149</v>
+        <v>0.007739342093565877</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>0.01815891142234239</v>
+        <v>0.01834851770126315</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>0.01701801172198347</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B11">
-        <v>2.542702532600868</v>
+        <v>2.477055720646894</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B15">
-        <v>0.02198232010707952</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B16">
-        <v>0.0994722274144087</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B17">
-        <v>0.01625160276571159</v>
+        <v>0.02095061942202305</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.09292387805031194</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.01579563890074885</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B20">
-        <v>32.79022202852632</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>32.79022202852632</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -1724,472 +2062,307 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>209115.6781418993</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B27">
-        <v>40913.82945166445</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B28">
-        <v>1704.742893819352</v>
+        <v>196192.1994272901</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>39857.52717725604</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>1660.730299052335</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>371937789.3923923</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33">
+        <v>335309001.8283048</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39">
         <v>100</v>
       </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40">
+        <v>0.07806677685727596</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41">
+        <v>0.01503412115351547</v>
+      </c>
+      <c r="C41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52">
-        <v>9.018117653923717</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>12093.47613626478</v>
-      </c>
-      <c r="E52">
-        <v>20126733.96341903</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>86.19320375350401</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53">
-        <v>8.914473018394579</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>11954.4866071275</v>
-      </c>
-      <c r="E53">
-        <v>19965820.86134986</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>85.20259090823538</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54">
-        <v>8.812733915186122</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="D54">
-        <v>11818.05243494289</v>
-      </c>
-      <c r="E54">
-        <v>19808029.91843414</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>84.23019072572833</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55">
-        <v>8.712833699068685</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>11684.08424712509</v>
-      </c>
-      <c r="E55">
-        <v>19653248.81501039</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>83.27536622539786</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56">
-        <v>8.614673592473483</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>11552.44958097879</v>
-      </c>
-      <c r="E56">
-        <v>19501316.10176986</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>82.33717331276218</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57">
-        <v>8.517956555013701</v>
-      </c>
-      <c r="C57">
-        <v>12.5</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G57">
-        <v>81.4127729405205</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" t="s">
         <v>108</v>
       </c>
-      <c r="B58">
-        <v>8.546174830209404</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>11460.59137080741</v>
-      </c>
-      <c r="E58">
-        <v>19395382.82052588</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>81.6824770669085</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59">
-        <v>8.451132665490242</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>11333.13792707572</v>
-      </c>
-      <c r="E59">
-        <v>19248521.98146494</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>80.77408476341613</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60">
-        <v>6.145082573697146</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>8240.678632979347</v>
-      </c>
-      <c r="E60">
-        <v>15728559.19260539</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>58.73336040657352</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B61">
-        <v>4.569071649889176</v>
+        <v>13.64991832932175</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>6127.216463934383</v>
+        <v>18304.81347798705</v>
       </c>
       <c r="E61">
-        <v>13370871.01226343</v>
+        <v>27489685.26117805</v>
       </c>
       <c r="F61">
         <v>0</v>
       </c>
       <c r="G61">
-        <v>43.6701913632616</v>
+        <v>130.4629454757689</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2197,25 +2370,25 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B62">
-        <v>4.536318042350857</v>
+        <v>13.39887433812282</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>6083.293221153346</v>
+        <v>17968.15846490946</v>
       </c>
       <c r="E62">
-        <v>13322285.00423805</v>
+        <v>27081995.23407607</v>
       </c>
       <c r="F62">
         <v>0</v>
       </c>
       <c r="G62">
-        <v>43.35713951845845</v>
+        <v>128.0635217029943</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -2223,25 +2396,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B63">
-        <v>4.503945058671606</v>
+        <v>13.15581646866565</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>6039.880402579797</v>
+        <v>17642.21300081001</v>
       </c>
       <c r="E63">
-        <v>13274280.12597966</v>
+        <v>26688215.53074061</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>43.04772559357354</v>
+        <v>125.7404275418864</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -2249,25 +2422,25 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B64">
-        <v>4.472003738676076</v>
+        <v>12.92035290962586</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D64">
-        <v>5997.046453639391</v>
+        <v>563.7016588664663</v>
       </c>
       <c r="E64">
-        <v>13226931.44501329</v>
+        <v>9953691.026075777</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="G64">
-        <v>42.74243741613079</v>
+        <v>123.4899181451708</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -2275,25 +2448,25 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B65">
-        <v>4.440386991847258</v>
+        <v>11.61825634377655</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>5954.64776380701</v>
+        <v>15580.31412213123</v>
       </c>
       <c r="E65">
-        <v>13180079.64569585</v>
+        <v>24218656.64999228</v>
       </c>
       <c r="F65">
         <v>0</v>
       </c>
       <c r="G65">
-        <v>42.44025143830053</v>
+        <v>111.0447628573425</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -2301,25 +2474,25 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B66">
-        <v>4.409153649591002</v>
+        <v>9.276212846842</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>5912.763227174526</v>
+        <v>12439.58695187206</v>
       </c>
       <c r="E66">
-        <v>13133811.38246208</v>
+        <v>20528170.28621273</v>
       </c>
       <c r="F66">
         <v>0</v>
       </c>
       <c r="G66">
-        <v>42.14172995784224</v>
+        <v>88.66002137606256</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -2327,25 +2500,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B67">
-        <v>4.378288825111254</v>
+        <v>6.165280453962315</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>5871.372880250693</v>
+        <v>8267.764394372543</v>
       </c>
       <c r="E67">
-        <v>13088104.0502434</v>
+        <v>15759027.53592782</v>
       </c>
       <c r="F67">
         <v>0</v>
       </c>
       <c r="G67">
-        <v>41.84673069000261</v>
+        <v>58.92640734562371</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -2353,25 +2526,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B68">
-        <v>4.34780375763793</v>
+        <v>6.105080551920921</v>
       </c>
       <c r="C68">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>8187.035121736994</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>15668235.32712333</v>
       </c>
       <c r="F68">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>41.5553610568925</v>
+        <v>58.35102979770082</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2379,25 +2552,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B69">
-        <v>10.06638495203542</v>
+        <v>6.045896970845131</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>13499.22354837854</v>
+        <v>8107.668755842737</v>
       </c>
       <c r="E69">
-        <v>21763679.27687195</v>
+        <v>15579031.27558782</v>
       </c>
       <c r="F69">
         <v>0</v>
       </c>
       <c r="G69">
-        <v>96.2123142022311</v>
+        <v>57.7853660241407</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -2405,25 +2578,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B70">
-        <v>9.892246225099244</v>
+        <v>5.9876915338538</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>13265.70003278259</v>
+        <v>8029.614100728623</v>
       </c>
       <c r="E70">
-        <v>21490556.29018191</v>
+        <v>15491355.06410149</v>
       </c>
       <c r="F70">
         <v>0</v>
       </c>
       <c r="G70">
-        <v>94.54793418988392</v>
+        <v>57.229051138631</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2431,25 +2604,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B71">
-        <v>9.722514965356615</v>
+        <v>5.930453816743045</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>13038.08701884253</v>
+        <v>7952.857177328758</v>
       </c>
       <c r="E71">
-        <v>21224803.40740003</v>
+        <v>15405188.32786324</v>
       </c>
       <c r="F71">
         <v>0</v>
       </c>
       <c r="G71">
-        <v>92.92567978871516</v>
+        <v>56.68198550890215</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -2457,10 +2630,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B72">
-        <v>9.558227757851759</v>
+        <v>5.874160752754944</v>
       </c>
       <c r="C72">
         <v>12.5</v>
@@ -2475,7 +2648,7 @@
         <v>16916025.69007904</v>
       </c>
       <c r="G72">
-        <v>91.35545845273612</v>
+        <v>56.14394866790747</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -2483,25 +2656,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B73">
-        <v>9.398028835051212</v>
+        <v>9.526376866434548</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>12602.94462838038</v>
+        <v>12775.06190542606</v>
       </c>
       <c r="E73">
-        <v>20718003.17416135</v>
+        <v>20918266.91211979</v>
       </c>
       <c r="F73">
         <v>0</v>
       </c>
       <c r="G73">
-        <v>89.82431205124385</v>
+        <v>91.05103457194322</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -2509,25 +2682,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B74">
-        <v>9.242813048554448</v>
+        <v>9.374124827351716</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>12394.79715437249</v>
+        <v>12570.8888759752</v>
       </c>
       <c r="E74">
-        <v>20476162.07385932</v>
+        <v>20680733.83934183</v>
       </c>
       <c r="F74">
         <v>0</v>
       </c>
       <c r="G74">
-        <v>88.34079338086421</v>
+        <v>89.59584275363255</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2535,27 +2708,131 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B75">
-        <v>9.091399389496097</v>
+        <v>9.225820669383163</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>12191.74840930206</v>
+        <v>12372.01003405621</v>
       </c>
       <c r="E75">
-        <v>20240608.84944247</v>
+        <v>20449709.24449027</v>
       </c>
       <c r="F75">
         <v>0</v>
       </c>
       <c r="G75">
-        <v>86.89361461616916</v>
+        <v>88.1783839228849</v>
       </c>
       <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76">
+        <v>9.08198253555928</v>
+      </c>
+      <c r="C76">
+        <v>12.5</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G76">
+        <v>86.80361037789667</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77">
+        <v>8.941810037098039</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>11991.14609594921</v>
+      </c>
+      <c r="E77">
+        <v>20008246.50484437</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>85.46387217707037</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78">
+        <v>8.805718865186405</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>11808.64511259227</v>
+      </c>
+      <c r="E78">
+        <v>19797155.99559797</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>84.16314240620419</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79">
+        <v>8.67304005660262</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>11630.72017670524</v>
+      </c>
+      <c r="E79">
+        <v>19591637.81303129</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>82.89502726057192</v>
+      </c>
+      <c r="H79">
         <v>0</v>
       </c>
     </row>
@@ -2566,63 +2843,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="R1" s="2" t="s">
+      <c r="A1" t="s">
         <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2630,55 +2907,55 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F2">
-        <v>48.95272656908845</v>
+        <v>48.86278277382081</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K2">
         <v>4.865822962046021</v>
       </c>
       <c r="L2">
-        <v>11.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M2">
-        <v>7.249328333333335</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N2">
         <v>4865822.962046022</v>
       </c>
       <c r="O2">
-        <v>4336559.807486307</v>
+        <v>4271748.703108184</v>
       </c>
       <c r="P2">
-        <v>38.47785298620752</v>
+        <v>42.24438697831445</v>
       </c>
       <c r="Q2">
-        <v>0.02929032999738784</v>
+        <v>0.03253431715376883</v>
       </c>
       <c r="R2">
-        <v>64.7348382535332</v>
+        <v>64.47053873969922</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2686,55 +2963,55 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F3">
-        <v>48.77559490180905</v>
+        <v>48.86278522240621</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K3">
         <v>4.865822962046021</v>
       </c>
       <c r="L3">
-        <v>1.666666666666668</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="M3">
-        <v>1.035618333333334</v>
+        <v>2.589045833333333</v>
       </c>
       <c r="N3">
-        <v>4865822.962046022</v>
+        <v>4271748.703108184</v>
       </c>
       <c r="O3">
-        <v>4794198.453627313</v>
+        <v>4069304.927154007</v>
       </c>
       <c r="P3">
-        <v>38.06465037729529</v>
+        <v>44.23936491737059</v>
       </c>
       <c r="Q3">
-        <v>0.02892830875350846</v>
+        <v>0.03411488712123179</v>
       </c>
       <c r="R3">
-        <v>61.65634640098574</v>
+        <v>65.97527728985341</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2742,55 +3019,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F4">
-        <v>48.77559590012213</v>
+        <v>48.5932494822047</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>4.865822962046021</v>
       </c>
       <c r="L4">
-        <v>9.999999999999998</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="M4">
-        <v>6.213709999999999</v>
+        <v>5.695900833333334</v>
       </c>
       <c r="N4">
-        <v>4794198.453627313</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O4">
-        <v>4340504.755143139</v>
+        <v>4469916.489068738</v>
       </c>
       <c r="P4">
-        <v>38.13649325564026</v>
+        <v>40.24060014056434</v>
       </c>
       <c r="Q4">
-        <v>0.02903005975330255</v>
+        <v>0.03095303720347287</v>
       </c>
       <c r="R4">
-        <v>64.70623300955242</v>
+        <v>63.09720839781258</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2798,55 +3075,55 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="E5" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F5">
-        <v>48.59961102550478</v>
+        <v>48.59324965807246</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K5">
         <v>4.865822962046021</v>
       </c>
       <c r="L5">
-        <v>3.333333333333336</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M5">
-        <v>2.071236666666668</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N5">
-        <v>4865822.962046022</v>
+        <v>4469916.489068738</v>
       </c>
       <c r="O5">
-        <v>4722547.955580813</v>
+        <v>4078596.630496888</v>
       </c>
       <c r="P5">
-        <v>37.97508248034337</v>
+        <v>43.90002997136786</v>
       </c>
       <c r="Q5">
-        <v>0.02886773547756429</v>
+        <v>0.0338511694889693</v>
       </c>
       <c r="R5">
-        <v>62.10810798775364</v>
+        <v>65.90378051947927</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2854,55 +3131,55 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F6">
-        <v>48.59961111395481</v>
+        <v>48.32860599700735</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K6">
         <v>4.865822962046021</v>
       </c>
       <c r="L6">
-        <v>8.333333333333332</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>5.178091666666666</v>
+        <v>3.106855</v>
       </c>
       <c r="N6">
-        <v>4722547.955580813</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O6">
-        <v>4344391.794437824</v>
+        <v>4656127.234382963</v>
       </c>
       <c r="P6">
-        <v>38.0349337194756</v>
+        <v>38.49986867434873</v>
       </c>
       <c r="Q6">
-        <v>0.02895234059105389</v>
+        <v>0.02958125665994566</v>
       </c>
       <c r="R6">
-        <v>64.67808472271173</v>
+        <v>61.88613799936822</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2910,55 +3187,55 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F7">
-        <v>48.42555342398909</v>
+        <v>48.3286060071518</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>4.865822962046021</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="M7">
-        <v>3.106855</v>
+        <v>7.7671375</v>
       </c>
       <c r="N7">
-        <v>4865822.962046022</v>
+        <v>4656127.234382963</v>
       </c>
       <c r="O7">
-        <v>4650847.311906654</v>
+        <v>4087662.82751308</v>
       </c>
       <c r="P7">
-        <v>37.88677100784726</v>
+        <v>43.56885747469899</v>
       </c>
       <c r="Q7">
-        <v>0.02880829329254438</v>
+        <v>0.03359383443470648</v>
       </c>
       <c r="R7">
-        <v>62.57027448691073</v>
+        <v>65.83424252313968</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -2966,55 +3243,55 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F8">
-        <v>48.42555343102754</v>
+        <v>48.06875874908656</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K8">
         <v>4.865822962046021</v>
       </c>
       <c r="L8">
-        <v>6.666666666666664</v>
+        <v>2.5</v>
       </c>
       <c r="M8">
-        <v>4.142473333333332</v>
+        <v>1.5534275</v>
       </c>
       <c r="N8">
-        <v>4650847.311906654</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O8">
-        <v>4348223.961192051</v>
+        <v>4763165.653954888</v>
       </c>
       <c r="P8">
-        <v>37.93464022592449</v>
+        <v>37.47596246755862</v>
       </c>
       <c r="Q8">
-        <v>0.02887559374228354</v>
+        <v>0.02877644436443457</v>
       </c>
       <c r="R8">
-        <v>64.65036972930982</v>
+        <v>61.22246834866992</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -3022,167 +3299,167 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F9">
-        <v>48.25346214391424</v>
+        <v>48.06875874958148</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K9">
         <v>4.865822962046021</v>
       </c>
       <c r="L9">
-        <v>8.333333333333336</v>
+        <v>15</v>
       </c>
       <c r="M9">
-        <v>5.178091666666668</v>
+        <v>9.320565</v>
       </c>
       <c r="N9">
-        <v>4865822.962046022</v>
+        <v>4763165.653954888</v>
       </c>
       <c r="O9">
-        <v>4504622.583510358</v>
+        <v>4096513.551423286</v>
       </c>
       <c r="P9">
-        <v>37.8477136319615</v>
+        <v>43.24555720011831</v>
       </c>
       <c r="Q9">
-        <v>0.02879353408091034</v>
+        <v>0.0333426529778781</v>
       </c>
       <c r="R9">
-        <v>63.54879853627121</v>
+        <v>65.76656910638809</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D10" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="E10" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F10">
-        <v>48.25346214440003</v>
+        <v>47.81356201798832</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K10">
         <v>4.865822962046021</v>
       </c>
       <c r="L10">
-        <v>3.333333333333329</v>
+        <v>15.75</v>
       </c>
       <c r="M10">
-        <v>2.071236666666664</v>
+        <v>9.786593249999999</v>
       </c>
       <c r="N10">
-        <v>4504622.583510358</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O10">
-        <v>4352005.453747332</v>
+        <v>4187124.927403578</v>
       </c>
       <c r="P10">
-        <v>37.87172378201949</v>
+        <v>42.1296984083516</v>
       </c>
       <c r="Q10">
-        <v>0.02882730572600047</v>
+        <v>0.0324637791216279</v>
       </c>
       <c r="R10">
-        <v>64.62305611684442</v>
+        <v>65.08554070727031</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>182</v>
       </c>
       <c r="E11" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F11">
-        <v>48.08330918770434</v>
+        <v>47.81356201800968</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K11">
         <v>4.865822962046021</v>
       </c>
       <c r="L11">
-        <v>11.66666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="M11">
-        <v>7.249328333333335</v>
+        <v>0.3106855</v>
       </c>
       <c r="N11">
-        <v>4865822.962046022</v>
+        <v>4187124.927403578</v>
       </c>
       <c r="O11">
-        <v>4355751.707740526</v>
+        <v>4163863.477126516</v>
       </c>
       <c r="P11">
-        <v>37.81023271059158</v>
+        <v>42.35371550130591</v>
       </c>
       <c r="Q11">
-        <v>0.02878010827224394</v>
+        <v>0.03264111270750891</v>
       </c>
       <c r="R11">
-        <v>64.59603113903587</v>
+        <v>65.25835161662208</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -3190,55 +3467,55 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F12">
-        <v>47.91506651192051</v>
+        <v>47.58408367578394</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K12">
         <v>4.865822962046021</v>
       </c>
       <c r="L12">
-        <v>11.81818181818182</v>
+        <v>15.25</v>
       </c>
       <c r="M12">
-        <v>7.343475454545456</v>
+        <v>9.475907749999999</v>
       </c>
       <c r="N12">
         <v>4865822.962046022</v>
       </c>
       <c r="O12">
-        <v>4352463.640046223</v>
+        <v>4216824.582714224</v>
       </c>
       <c r="P12">
-        <v>37.6823003152677</v>
+        <v>41.64682015557088</v>
       </c>
       <c r="Q12">
-        <v>0.02868307208301009</v>
+        <v>0.0320856268816049</v>
       </c>
       <c r="R12">
-        <v>64.61974900119652</v>
+        <v>64.86732069663434</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -3246,55 +3523,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>47.74626648059002</v>
+        <v>39.47142340298675</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K13">
         <v>4.865822962046021</v>
       </c>
       <c r="L13">
-        <v>3.93181818181818</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>2.443117795454544</v>
+        <v>0.621371</v>
       </c>
       <c r="N13">
-        <v>4865822.962046022</v>
+        <v>4216824.582714224</v>
       </c>
       <c r="O13">
-        <v>4702216.066588552</v>
+        <v>4184956.947409213</v>
       </c>
       <c r="P13">
-        <v>37.32516224288786</v>
+        <v>34.79638921914457</v>
       </c>
       <c r="Q13">
-        <v>0.02837580920975124</v>
+        <v>0.02681332814380802</v>
       </c>
       <c r="R13">
-        <v>62.23812150506072</v>
+        <v>65.10158879345772</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -3302,55 +3579,55 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="E14" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F14">
-        <v>47.74626648059013</v>
+        <v>39.28820400357699</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K14">
         <v>4.865822962046021</v>
       </c>
       <c r="L14">
-        <v>7.88636363636364</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="M14">
-        <v>4.900357659090911</v>
+        <v>9.424126833333336</v>
       </c>
       <c r="N14">
-        <v>4702216.066588552</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O14">
-        <v>4356156.422884206</v>
+        <v>4430711.39240246</v>
       </c>
       <c r="P14">
-        <v>37.38087783712439</v>
+        <v>32.80857408813353</v>
       </c>
       <c r="Q14">
-        <v>0.02845325338268903</v>
+        <v>0.02524226739850578</v>
       </c>
       <c r="R14">
-        <v>64.5931136066735</v>
+        <v>63.36194224826892</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -3358,55 +3635,55 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F15">
-        <v>47.57934367740155</v>
+        <v>39.28820400357712</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>4.865822962046021</v>
       </c>
       <c r="L15">
-        <v>7.86363636363636</v>
+        <v>1.083333333333329</v>
       </c>
       <c r="M15">
-        <v>4.886235590909089</v>
+        <v>0.673151916666664</v>
       </c>
       <c r="N15">
-        <v>4865822.962046022</v>
+        <v>4430711.39240246</v>
       </c>
       <c r="O15">
-        <v>4535236.113741167</v>
+        <v>4398070.61013838</v>
       </c>
       <c r="P15">
-        <v>37.30564340651419</v>
+        <v>33.03988493684162</v>
       </c>
       <c r="Q15">
-        <v>0.02837818761488594</v>
+        <v>0.02542528710607268</v>
       </c>
       <c r="R15">
-        <v>63.33969281564816</v>
+        <v>63.58491082906026</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -3414,55 +3691,55 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F16">
-        <v>39.46668340460315</v>
+        <v>39.16643027967964</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K16">
         <v>4.865822962046021</v>
       </c>
       <c r="L16">
-        <v>3.95454545454546</v>
+        <v>15.08333333333334</v>
       </c>
       <c r="M16">
-        <v>2.457239863636367</v>
+        <v>9.372345916666671</v>
       </c>
       <c r="N16">
-        <v>4535236.113741167</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O16">
-        <v>4413960.254057059</v>
+        <v>4435928.748810861</v>
       </c>
       <c r="P16">
-        <v>30.96800829905313</v>
+        <v>32.67032441415775</v>
       </c>
       <c r="Q16">
-        <v>0.02356707530590499</v>
+        <v>0.02513510833286266</v>
       </c>
       <c r="R16">
-        <v>64.18043133242925</v>
+        <v>63.32651955332852</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3470,55 +3747,55 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="E17" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>39.34530861975033</v>
+        <v>39.16643027968009</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K17">
         <v>4.865822962046021</v>
       </c>
       <c r="L17">
-        <v>11.81818181818182</v>
+        <v>1.166666666666657</v>
       </c>
       <c r="M17">
-        <v>7.343475454545456</v>
+        <v>0.7249328333333274</v>
       </c>
       <c r="N17">
-        <v>4865822.962046022</v>
+        <v>4435928.748810861</v>
       </c>
       <c r="O17">
-        <v>4521904.191755312</v>
+        <v>4401018.831520611</v>
       </c>
       <c r="P17">
-        <v>30.94270431704686</v>
+        <v>32.91651638266229</v>
       </c>
       <c r="Q17">
-        <v>0.02353899993898193</v>
+        <v>0.02532989333314859</v>
       </c>
       <c r="R17">
-        <v>63.43050245560413</v>
+        <v>63.5646748188657</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3526,55 +3803,55 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F18">
-        <v>39.25506246246415</v>
+        <v>39.04584559597336</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K18">
         <v>4.865822962046021</v>
       </c>
       <c r="L18">
-        <v>0.3939393939393909</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="M18">
-        <v>0.2447825151515133</v>
+        <v>9.320565000000007</v>
       </c>
       <c r="N18">
         <v>4865822.962046022</v>
       </c>
       <c r="O18">
-        <v>4854789.212054112</v>
+        <v>4441076.081944307</v>
       </c>
       <c r="P18">
-        <v>30.60556774008359</v>
+        <v>32.53386171711234</v>
       </c>
       <c r="Q18">
-        <v>0.02325458299320541</v>
+        <v>0.02502934301097571</v>
       </c>
       <c r="R18">
-        <v>61.2819140309153</v>
+        <v>63.29163042862624</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3582,55 +3859,55 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="E19" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F19">
-        <v>39.25506246246442</v>
+        <v>39.04584559597345</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>4.865822962046021</v>
       </c>
       <c r="L19">
-        <v>11.42424242424243</v>
+        <v>1.249999999999986</v>
       </c>
       <c r="M19">
-        <v>7.098692939393943</v>
+        <v>0.7767137499999913</v>
       </c>
       <c r="N19">
-        <v>4854789.212054112</v>
+        <v>4441076.081944307</v>
       </c>
       <c r="O19">
-        <v>4523488.796483492</v>
+        <v>4403927.801596629</v>
       </c>
       <c r="P19">
-        <v>30.67145615131222</v>
+        <v>32.79458110273955</v>
       </c>
       <c r="Q19">
-        <v>0.02333252813448057</v>
+        <v>0.02523561252106806</v>
       </c>
       <c r="R19">
-        <v>63.41968855245604</v>
+        <v>63.54472714630007</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -3638,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="C20" t="s">
         <v>204</v>
@@ -3647,46 +3924,46 @@
         <v>205</v>
       </c>
       <c r="E20" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F20">
-        <v>39.16546323905106</v>
+        <v>38.92642987856389</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K20">
         <v>4.865822962046021</v>
       </c>
       <c r="L20">
-        <v>4.742424242424242</v>
+        <v>15.41666666666669</v>
       </c>
       <c r="M20">
-        <v>2.946804893939394</v>
+        <v>9.579469583333347</v>
       </c>
       <c r="N20">
         <v>4865822.962046022</v>
       </c>
       <c r="O20">
-        <v>4731939.229730661</v>
+        <v>4431436.062867114</v>
       </c>
       <c r="P20">
-        <v>30.63597114961317</v>
+        <v>32.50141404588542</v>
       </c>
       <c r="Q20">
-        <v>0.02328791929709484</v>
+        <v>0.02500583493444001</v>
       </c>
       <c r="R20">
-        <v>62.04832936455576</v>
+        <v>63.35701861904475</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -3694,55 +3971,55 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
         <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E21" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F21">
-        <v>39.16546323905115</v>
+        <v>38.92642987856441</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K21">
         <v>4.865822962046021</v>
       </c>
       <c r="L21">
-        <v>7.075757575757578</v>
+        <v>0.8333333333333144</v>
       </c>
       <c r="M21">
-        <v>4.396670560606062</v>
+        <v>0.5178091666666549</v>
       </c>
       <c r="N21">
-        <v>4731939.229730661</v>
+        <v>4431436.062867114</v>
       </c>
       <c r="O21">
-        <v>4525058.832667484</v>
+        <v>4406799.311033905</v>
       </c>
       <c r="P21">
-        <v>30.67704291071613</v>
+        <v>32.67404384144189</v>
       </c>
       <c r="Q21">
-        <v>0.02333665375889065</v>
+        <v>0.02514241711008496</v>
       </c>
       <c r="R21">
-        <v>63.40897952312288</v>
+        <v>63.52505475959416</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -3750,55 +4027,55 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="C22" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D22" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E22" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F22">
-        <v>39.07650343160689</v>
+        <v>38.80816380760871</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K22">
         <v>4.865822962046021</v>
       </c>
       <c r="L22">
-        <v>9.090909090909093</v>
+        <v>15.83333333333336</v>
       </c>
       <c r="M22">
-        <v>5.648827272727274</v>
+        <v>9.838374166666684</v>
       </c>
       <c r="N22">
         <v>4865822.962046022</v>
       </c>
       <c r="O22">
-        <v>4607039.580147291</v>
+        <v>4421887.933634564</v>
       </c>
       <c r="P22">
-        <v>30.66741974054591</v>
+        <v>32.46915265674014</v>
       </c>
       <c r="Q22">
-        <v>0.02332274090189485</v>
+        <v>0.02498245915618956</v>
       </c>
       <c r="R22">
-        <v>62.85777863301485</v>
+        <v>63.42198370568907</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -3806,55 +4083,55 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="E23" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F23">
-        <v>39.07650343160658</v>
+        <v>38.80816380760816</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K23">
         <v>4.865822962046021</v>
       </c>
       <c r="L23">
-        <v>2.727272727272734</v>
+        <v>0.416666666666643</v>
       </c>
       <c r="M23">
-        <v>1.694648181818186</v>
+        <v>0.2589045833333186</v>
       </c>
       <c r="N23">
-        <v>4607039.580147291</v>
+        <v>4421887.933634564</v>
       </c>
       <c r="O23">
-        <v>4526610.414341434</v>
+        <v>4409633.187231601</v>
       </c>
       <c r="P23">
-        <v>30.68335338834988</v>
+        <v>32.55488408917075</v>
       </c>
       <c r="Q23">
-        <v>0.02334133141934079</v>
+        <v>0.02505029119694339</v>
       </c>
       <c r="R23">
-        <v>63.39840169771319</v>
+        <v>63.50565809611707</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3862,335 +4139,335 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D24" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="E24" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F24">
-        <v>38.98817451411336</v>
+        <v>38.69102826915921</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K24">
         <v>4.865822962046021</v>
       </c>
       <c r="L24">
-        <v>11.81818181818181</v>
+        <v>16.25000000000003</v>
       </c>
       <c r="M24">
-        <v>7.343475454545449</v>
+        <v>10.09727875000002</v>
       </c>
       <c r="N24">
         <v>4865822.962046022</v>
       </c>
       <c r="O24">
-        <v>4528150.941042197</v>
+        <v>4412430.193866032</v>
       </c>
       <c r="P24">
-        <v>30.66183995430782</v>
+        <v>32.43707506892437</v>
       </c>
       <c r="Q24">
-        <v>0.02332484398184326</v>
+        <v>0.02495921391625393</v>
       </c>
       <c r="R24">
-        <v>63.38790447456379</v>
+        <v>63.48653120084359</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D25" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E25" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F25">
-        <v>38.9004700757539</v>
+        <v>38.5750046048706</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K25">
         <v>4.865822962046021</v>
       </c>
       <c r="L25">
-        <v>2.121212121212125</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M25">
-        <v>1.318059696969699</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N25">
         <v>4865822.962046022</v>
       </c>
       <c r="O25">
-        <v>4807168.102858045</v>
+        <v>4403061.378298423</v>
       </c>
       <c r="P25">
-        <v>30.36854336048954</v>
+        <v>32.40517885536858</v>
       </c>
       <c r="Q25">
-        <v>0.0230783662515439</v>
+        <v>0.02493609749287283</v>
       </c>
       <c r="R25">
-        <v>61.57562069245655</v>
+        <v>63.5506665045806</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E26" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F26">
-        <v>38.90047007575408</v>
+        <v>38.57500460487058</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>4.865822962046021</v>
       </c>
       <c r="L26">
-        <v>9.696969696969688</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M26">
-        <v>6.025415757575752</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N26">
-        <v>4807168.102858045</v>
+        <v>4403061.378298423</v>
       </c>
       <c r="O26">
-        <v>4529675.988140724</v>
+        <v>4153425.085857897</v>
       </c>
       <c r="P26">
-        <v>30.42415632772641</v>
+        <v>34.25184052096913</v>
       </c>
       <c r="Q26">
-        <v>0.02314391549929394</v>
+        <v>0.02639889221882216</v>
       </c>
       <c r="R26">
-        <v>63.37751786440531</v>
+        <v>65.33634787153724</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D27" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E27" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F27">
-        <v>38.81338254370156</v>
+        <v>38.38684408323018</v>
       </c>
       <c r="G27">
         <v>650</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I27">
         <v>9.525</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>4.865822962046021</v>
       </c>
       <c r="L27">
-        <v>6.969696969696983</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M27">
-        <v>4.330767575757585</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N27">
         <v>4865822.962046022</v>
       </c>
       <c r="O27">
-        <v>4671284.311111992</v>
+        <v>4642099.453951705</v>
       </c>
       <c r="P27">
-        <v>30.41184252881515</v>
+        <v>30.66760228762254</v>
       </c>
       <c r="Q27">
-        <v>0.02312274023825246</v>
+        <v>0.02356534586854096</v>
       </c>
       <c r="R27">
-        <v>62.43749193857644</v>
+        <v>61.97472358769908</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="C28" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D28" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E28" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F28">
-        <v>38.81338254370153</v>
+        <v>38.38684408323012</v>
       </c>
       <c r="G28">
         <v>650</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I28">
         <v>9.525</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K28">
         <v>4.865822962046021</v>
       </c>
       <c r="L28">
-        <v>4.848484848484844</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M28">
-        <v>3.012707878787876</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N28">
-        <v>4671284.311111992</v>
+        <v>4642099.453951705</v>
       </c>
       <c r="O28">
-        <v>4531186.387882071</v>
+        <v>4160674.10253235</v>
       </c>
       <c r="P28">
-        <v>30.4398581401474</v>
+        <v>34.02824615110477</v>
       </c>
       <c r="Q28">
-        <v>0.02315574157559715</v>
+        <v>0.0262253718082168</v>
       </c>
       <c r="R28">
-        <v>63.3672360435594</v>
+        <v>65.28215316451974</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F29">
-        <v>38.72690463916599</v>
+        <v>38.20169077235793</v>
       </c>
       <c r="G29">
         <v>650</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I29">
         <v>9.525</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>4.865822962046021</v>
       </c>
       <c r="L29">
-        <v>11.81818181818183</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M29">
-        <v>7.343475454545462</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N29">
         <v>4865822.962046022</v>
       </c>
       <c r="O29">
-        <v>4532681.101135243</v>
+        <v>4412125.875375135</v>
       </c>
       <c r="P29">
-        <v>30.45636700795024</v>
+        <v>32.02893208197189</v>
       </c>
       <c r="Q29">
-        <v>0.02316818275669781</v>
+        <v>0.02464520763683818</v>
       </c>
       <c r="R29">
-        <v>63.35706593097168</v>
+        <v>63.48861139772637</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -4198,55 +4475,55 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="D30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E30" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F30">
-        <v>38.6410288613653</v>
+        <v>38.20169077235801</v>
       </c>
       <c r="G30">
         <v>650</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>9.525</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>4.865822962046021</v>
       </c>
       <c r="L30">
-        <v>16.66666666666667</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="M30">
-        <v>10.35618333333334</v>
+        <v>5.178091666666663</v>
       </c>
       <c r="N30">
-        <v>4865822.962046022</v>
+        <v>4412125.875375135</v>
       </c>
       <c r="O30">
-        <v>4391091.449735745</v>
+        <v>4167786.967349901</v>
       </c>
       <c r="P30">
-        <v>30.50213133533921</v>
+        <v>33.80910471483357</v>
       </c>
       <c r="Q30">
-        <v>0.02321442690352209</v>
+        <v>0.02605532459860438</v>
       </c>
       <c r="R30">
-        <v>64.34275231227099</v>
+        <v>65.22910721841413</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -4254,55 +4531,55 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="E31" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F31">
-        <v>38.64102886136531</v>
+        <v>38.01946669556035</v>
       </c>
       <c r="G31">
         <v>650</v>
       </c>
       <c r="H31" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I31">
         <v>9.525</v>
       </c>
       <c r="J31" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K31">
         <v>4.865822962046021</v>
       </c>
       <c r="L31">
-        <v>8.333333333333336</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="M31">
-        <v>5.178091666666668</v>
+        <v>5.178091666666672</v>
       </c>
       <c r="N31">
-        <v>4391091.449735745</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O31">
-        <v>4133937.103348901</v>
+        <v>4646324.312066911</v>
       </c>
       <c r="P31">
-        <v>30.55120996535084</v>
+        <v>30.34791552378032</v>
       </c>
       <c r="Q31">
-        <v>0.02327364642818177</v>
+        <v>0.02331910139592562</v>
       </c>
       <c r="R31">
-        <v>66.25911036343361</v>
+        <v>61.94800353911928</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -4310,87 +4587,87 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="D32" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="E32" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F32">
-        <v>38.44220235364211</v>
+        <v>38.01946669556039</v>
       </c>
       <c r="G32">
         <v>650</v>
       </c>
       <c r="H32" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I32">
         <v>9.525</v>
       </c>
       <c r="J32" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K32">
         <v>4.865822962046021</v>
       </c>
       <c r="L32">
-        <v>8.333333333333332</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M32">
-        <v>5.178091666666666</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N32">
-        <v>4865822.962046022</v>
+        <v>4646324.312066911</v>
       </c>
       <c r="O32">
-        <v>4636710.743668576</v>
+        <v>4174721.581893245</v>
       </c>
       <c r="P32">
-        <v>30.15222956104614</v>
+        <v>33.59462772081157</v>
       </c>
       <c r="Q32">
-        <v>0.02292833943772314</v>
+        <v>0.02588891916725162</v>
       </c>
       <c r="R32">
-        <v>62.6626193272523</v>
+        <v>65.17751490951778</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E33" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F33">
-        <v>38.44220235364207</v>
+        <v>37.84008364202604</v>
       </c>
       <c r="G33">
         <v>650</v>
       </c>
       <c r="H33" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I33">
         <v>9.525</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K33">
         <v>4.865822962046021</v>
@@ -4402,219 +4679,219 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N33">
-        <v>4636710.743668576</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O33">
-        <v>4141818.268532108</v>
+        <v>4420809.07446864</v>
       </c>
       <c r="P33">
-        <v>30.24824012886473</v>
+        <v>31.66654234589742</v>
       </c>
       <c r="Q33">
-        <v>0.02304223788408494</v>
+        <v>0.02436507328101736</v>
       </c>
       <c r="R33">
-        <v>66.19755451376943</v>
+        <v>63.42933679265437</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="C34" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D34" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="E34" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F34">
-        <v>38.24681535226613</v>
+        <v>37.84008364202602</v>
       </c>
       <c r="G34">
         <v>650</v>
       </c>
       <c r="H34" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I34">
         <v>9.525</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K34">
         <v>4.865822962046021</v>
       </c>
       <c r="L34">
-        <v>16.66666666666666</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M34">
-        <v>10.35618333333333</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N34">
-        <v>4865822.962046022</v>
+        <v>4420809.07446864</v>
       </c>
       <c r="O34">
-        <v>4400914.935676467</v>
+        <v>4181527.042733391</v>
       </c>
       <c r="P34">
-        <v>30.19095038123345</v>
+        <v>33.38431597117621</v>
       </c>
       <c r="Q34">
-        <v>0.02297678885652028</v>
+        <v>0.02572576165380728</v>
       </c>
       <c r="R34">
-        <v>64.27287523159232</v>
+        <v>65.12700231683168</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D35" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F35">
-        <v>38.2468153522661</v>
+        <v>37.66346920984691</v>
       </c>
       <c r="G35">
         <v>650</v>
       </c>
       <c r="H35" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I35">
         <v>9.525</v>
       </c>
       <c r="J35" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K35">
         <v>4.865822962046021</v>
       </c>
       <c r="L35">
-        <v>8.333333333333343</v>
+        <v>8.333333333333336</v>
       </c>
       <c r="M35">
-        <v>5.178091666666672</v>
+        <v>5.178091666666668</v>
       </c>
       <c r="N35">
-        <v>4400914.935676467</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O35">
-        <v>4149551.629908944</v>
+        <v>4650377.760059973</v>
       </c>
       <c r="P35">
-        <v>30.23952831394146</v>
+        <v>30.03890510454428</v>
       </c>
       <c r="Q35">
-        <v>0.02303500628469935</v>
+        <v>0.02308109758783787</v>
       </c>
       <c r="R35">
-        <v>66.13731954481381</v>
+        <v>61.92240002987046</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="C36" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E36" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F36">
-        <v>38.0547808030154</v>
+        <v>37.66346920984687</v>
       </c>
       <c r="G36">
         <v>650</v>
       </c>
       <c r="H36" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I36">
         <v>9.525</v>
       </c>
       <c r="J36" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K36">
         <v>4.865822962046021</v>
       </c>
       <c r="L36">
-        <v>8.333333333333329</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M36">
-        <v>5.178091666666663</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N36">
-        <v>4865822.962046022</v>
+        <v>4650377.760059973</v>
       </c>
       <c r="O36">
-        <v>4641270.4856087</v>
+        <v>4188168.48133387</v>
       </c>
       <c r="P36">
-        <v>29.84835457948474</v>
+        <v>33.17833081804088</v>
       </c>
       <c r="Q36">
-        <v>0.02269687462821422</v>
+        <v>0.0255659808356964</v>
       </c>
       <c r="R36">
-        <v>62.63278889502322</v>
+        <v>65.07782021497837</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="D37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E37" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F37">
-        <v>38.05478080301538</v>
+        <v>37.48954278657779</v>
       </c>
       <c r="G37">
         <v>650</v>
       </c>
       <c r="H37" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I37">
         <v>9.525</v>
       </c>
       <c r="J37" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K37">
         <v>4.865822962046021</v>
@@ -4626,19 +4903,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N37">
-        <v>4641270.4856087</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O37">
-        <v>4157064.027729862</v>
+        <v>4429135.882351197</v>
       </c>
       <c r="P37">
-        <v>29.94339755021512</v>
+        <v>31.31714090994992</v>
       </c>
       <c r="Q37">
-        <v>0.02280885755269644</v>
+        <v>0.02409501796322748</v>
       </c>
       <c r="R37">
-        <v>66.07896282478444</v>
+        <v>63.37265069959508</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -4646,55 +4923,55 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C38" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="D38" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="E38" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F38">
-        <v>37.86599117752703</v>
+        <v>37.48954278657779</v>
       </c>
       <c r="G38">
         <v>650</v>
       </c>
       <c r="H38" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I38">
         <v>9.525</v>
       </c>
       <c r="J38" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K38">
         <v>4.865822962046021</v>
       </c>
       <c r="L38">
-        <v>16.66666666666667</v>
+        <v>8.333333333333329</v>
       </c>
       <c r="M38">
-        <v>10.35618333333334</v>
+        <v>5.178091666666663</v>
       </c>
       <c r="N38">
-        <v>4865822.962046022</v>
+        <v>4429135.882351197</v>
       </c>
       <c r="O38">
-        <v>4410293.334579322</v>
+        <v>4194687.081148683</v>
       </c>
       <c r="P38">
-        <v>29.89033858760758</v>
+        <v>32.97625050523194</v>
       </c>
       <c r="Q38">
-        <v>0.02274724987937389</v>
+        <v>0.0254092441014044</v>
       </c>
       <c r="R38">
-        <v>64.20637615439065</v>
+        <v>65.02965596569788</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -4702,55 +4979,55 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="D39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E39" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F39">
-        <v>37.86599117752701</v>
+        <v>37.318236972821</v>
       </c>
       <c r="G39">
         <v>650</v>
       </c>
       <c r="H39" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I39">
         <v>9.525</v>
       </c>
       <c r="J39" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K39">
         <v>4.865822962046021</v>
       </c>
       <c r="L39">
-        <v>8.333333333333336</v>
+        <v>8.333333333333343</v>
       </c>
       <c r="M39">
-        <v>5.178091666666668</v>
+        <v>5.178091666666672</v>
       </c>
       <c r="N39">
-        <v>4410293.334579322</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O39">
-        <v>4164437.083456788</v>
+        <v>4654270.613134009</v>
       </c>
       <c r="P39">
-        <v>29.93843282903402</v>
+        <v>29.73995684583101</v>
       </c>
       <c r="Q39">
-        <v>0.02280451752366624</v>
+        <v>0.02285085957060958</v>
       </c>
       <c r="R39">
-        <v>66.02183846440246</v>
+        <v>61.8978407753484</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -4758,335 +5035,55 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="D40" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="E40" t="s">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="F40">
-        <v>37.68036572592165</v>
+        <v>37.31823697282099</v>
       </c>
       <c r="G40">
         <v>650</v>
       </c>
       <c r="H40" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I40">
         <v>9.525</v>
       </c>
       <c r="J40" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K40">
         <v>4.865822962046021</v>
       </c>
       <c r="L40">
-        <v>8.333333333333332</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M40">
-        <v>5.178091666666666</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N40">
-        <v>4865822.962046022</v>
+        <v>4654270.613134009</v>
       </c>
       <c r="O40">
-        <v>4645631.06209994</v>
+        <v>4201054.628480863</v>
       </c>
       <c r="P40">
-        <v>29.55468125526173</v>
+        <v>32.77819126028395</v>
       </c>
       <c r="Q40">
-        <v>0.0224731926876343</v>
+        <v>0.02525564443044986</v>
       </c>
       <c r="R40">
-        <v>62.60430124444154</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="A41">
-        <v>3</v>
-      </c>
-      <c r="B41" t="s">
-        <v>181</v>
-      </c>
-      <c r="C41" t="s">
-        <v>225</v>
-      </c>
-      <c r="D41" t="s">
-        <v>252</v>
-      </c>
-      <c r="E41" t="s">
-        <v>255</v>
-      </c>
-      <c r="F41">
-        <v>37.68036572592172</v>
-      </c>
-      <c r="G41">
-        <v>650</v>
-      </c>
-      <c r="H41" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41">
-        <v>9.525</v>
-      </c>
-      <c r="J41" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L41">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M41">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N41">
-        <v>4645631.06209994</v>
-      </c>
-      <c r="O41">
-        <v>4171606.781266716</v>
-      </c>
-      <c r="P41">
-        <v>29.64878911296666</v>
-      </c>
-      <c r="Q41">
-        <v>0.02258335596210616</v>
-      </c>
-      <c r="R41">
-        <v>65.96643150115214</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18">
-      <c r="A42">
-        <v>3</v>
-      </c>
-      <c r="B42" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" t="s">
-        <v>226</v>
-      </c>
-      <c r="D42" t="s">
-        <v>227</v>
-      </c>
-      <c r="E42" t="s">
-        <v>255</v>
-      </c>
-      <c r="F42">
-        <v>37.49780602363148</v>
-      </c>
-      <c r="G42">
-        <v>650</v>
-      </c>
-      <c r="H42" t="s">
-        <v>86</v>
-      </c>
-      <c r="I42">
-        <v>9.525</v>
-      </c>
-      <c r="J42" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L42">
-        <v>16.66666666666666</v>
-      </c>
-      <c r="M42">
-        <v>10.35618333333333</v>
-      </c>
-      <c r="N42">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O42">
-        <v>4419256.992265442</v>
-      </c>
-      <c r="P42">
-        <v>29.59970367826973</v>
-      </c>
-      <c r="Q42">
-        <v>0.02252535442598358</v>
-      </c>
-      <c r="R42">
-        <v>64.14301040125868</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18">
-      <c r="A43">
-        <v>3</v>
-      </c>
-      <c r="B43" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" t="s">
-        <v>253</v>
-      </c>
-      <c r="E43" t="s">
-        <v>255</v>
-      </c>
-      <c r="F43">
-        <v>37.49780602363148</v>
-      </c>
-      <c r="G43">
-        <v>650</v>
-      </c>
-      <c r="H43" t="s">
-        <v>86</v>
-      </c>
-      <c r="I43">
-        <v>9.525</v>
-      </c>
-      <c r="J43" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L43">
-        <v>8.333333333333343</v>
-      </c>
-      <c r="M43">
-        <v>5.178091666666672</v>
-      </c>
-      <c r="N43">
-        <v>4419256.992265442</v>
-      </c>
-      <c r="O43">
-        <v>4178644.739062462</v>
-      </c>
-      <c r="P43">
-        <v>29.6473302814506</v>
-      </c>
-      <c r="Q43">
-        <v>0.02258172027535455</v>
-      </c>
-      <c r="R43">
-        <v>65.91217806736719</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18">
-      <c r="A44">
-        <v>3</v>
-      </c>
-      <c r="B44" t="s">
-        <v>184</v>
-      </c>
-      <c r="C44" t="s">
-        <v>228</v>
-      </c>
-      <c r="D44" t="s">
-        <v>229</v>
-      </c>
-      <c r="E44" t="s">
-        <v>255</v>
-      </c>
-      <c r="F44">
-        <v>37.31823697282096</v>
-      </c>
-      <c r="G44">
-        <v>650</v>
-      </c>
-      <c r="H44" t="s">
-        <v>86</v>
-      </c>
-      <c r="I44">
-        <v>9.525</v>
-      </c>
-      <c r="J44" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L44">
-        <v>8.333333333333329</v>
-      </c>
-      <c r="M44">
-        <v>5.178091666666663</v>
-      </c>
-      <c r="N44">
-        <v>4865822.962046022</v>
-      </c>
-      <c r="O44">
-        <v>4649805.566991739</v>
-      </c>
-      <c r="P44">
-        <v>29.27064473743426</v>
-      </c>
-      <c r="Q44">
-        <v>0.02225686201782282</v>
-      </c>
-      <c r="R44">
-        <v>62.57706558684811</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18">
-      <c r="A45">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" t="s">
-        <v>229</v>
-      </c>
-      <c r="D45" t="s">
-        <v>254</v>
-      </c>
-      <c r="E45" t="s">
-        <v>255</v>
-      </c>
-      <c r="F45">
-        <v>37.31823697282105</v>
-      </c>
-      <c r="G45">
-        <v>650</v>
-      </c>
-      <c r="H45" t="s">
-        <v>86</v>
-      </c>
-      <c r="I45">
-        <v>9.525</v>
-      </c>
-      <c r="J45" t="s">
-        <v>85</v>
-      </c>
-      <c r="K45">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L45">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M45">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N45">
-        <v>4649805.566991739</v>
-      </c>
-      <c r="O45">
-        <v>4185495.351773777</v>
-      </c>
-      <c r="P45">
-        <v>29.36384816758093</v>
-      </c>
-      <c r="Q45">
-        <v>0.02236525950281841</v>
-      </c>
-      <c r="R45">
-        <v>65.85959873384216</v>
+        <v>64.98271090556716</v>
       </c>
     </row>
   </sheetData>
@@ -5096,62 +5093,62 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
         <v>257</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>258</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>259</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>260</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="J1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" t="s">
         <v>261</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" t="s">
         <v>262</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" t="s">
         <v>263</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>264</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" t="s">
         <v>265</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>266</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" t="s">
         <v>267</v>
       </c>
     </row>
@@ -5160,40 +5157,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>230</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>268</v>
       </c>
       <c r="F2">
-        <v>11.66666666666667</v>
+        <v>17.5</v>
       </c>
       <c r="G2">
-        <v>7.249328333333333</v>
+        <v>10.8739925</v>
       </c>
       <c r="H2">
-        <v>1.122046778565359</v>
+        <v>1.195738104946853</v>
       </c>
       <c r="I2">
-        <v>86.19320375350401</v>
+        <v>130.4629454757689</v>
       </c>
       <c r="J2">
-        <v>9.018117653923717</v>
+        <v>13.64991832932175</v>
       </c>
       <c r="K2">
-        <v>12093.47613626478</v>
+        <v>18304.81347798705</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>9.018117653923717</v>
+        <v>13.64991832932175</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -5202,13 +5199,13 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>20126733.96341903</v>
+        <v>27489685.26117805</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>20126733.96341903</v>
+        <v>27489685.26117805</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -5216,40 +5213,40 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
         <v>268</v>
       </c>
       <c r="F3">
-        <v>23.33333333333333</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>14.49865666666667</v>
+        <v>21.747985</v>
       </c>
       <c r="H3">
-        <v>1.121026985693409</v>
+        <v>1.193014019984915</v>
       </c>
       <c r="I3">
-        <v>85.20259090823538</v>
+        <v>128.0635217029943</v>
       </c>
       <c r="J3">
-        <v>8.914473018394579</v>
+        <v>13.39887433812282</v>
       </c>
       <c r="K3">
-        <v>11954.4866071275</v>
+        <v>17968.15846490946</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>8.914473018394579</v>
+        <v>13.39887433812282</v>
       </c>
       <c r="N3">
         <v>0.78</v>
@@ -5258,13 +5255,13 @@
         <v>0.357</v>
       </c>
       <c r="P3">
-        <v>19965820.86134986</v>
+        <v>27081995.23407607</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>19965820.86134986</v>
+        <v>27081995.23407607</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -5272,40 +5269,40 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>268</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>52.5</v>
       </c>
       <c r="G4">
-        <v>21.747985</v>
+        <v>32.6219775</v>
       </c>
       <c r="H4">
-        <v>1.120023973960128</v>
+        <v>1.190367984681939</v>
       </c>
       <c r="I4">
-        <v>84.23019072572833</v>
+        <v>125.7404275418864</v>
       </c>
       <c r="J4">
-        <v>8.812733915186122</v>
+        <v>13.15581646866565</v>
       </c>
       <c r="K4">
-        <v>11818.05243494289</v>
+        <v>17642.21300081001</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>8.812733915186122</v>
+        <v>13.15581646866565</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -5314,54 +5311,51 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>19808029.91843414</v>
+        <v>26688215.53074061</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>19808029.91843414</v>
+        <v>26688215.53074061</v>
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5">
-        <v>0</v>
-      </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="F5">
-        <v>46.66666666666666</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>28.99731333333333</v>
+        <v>43.49597</v>
       </c>
       <c r="H5">
-        <v>1.119036877003933</v>
+        <v>1.187796134680294</v>
       </c>
       <c r="I5">
-        <v>83.27536622539786</v>
+        <v>123.4899181451708</v>
       </c>
       <c r="J5">
-        <v>8.712833699068685</v>
+        <v>12.92035290962586</v>
       </c>
       <c r="K5">
-        <v>11684.08424712509</v>
+        <v>17326.45165886647</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>8.712833699068685</v>
+        <v>12.92035290962586</v>
       </c>
       <c r="N5">
         <v>0.78</v>
@@ -5370,54 +5364,54 @@
         <v>0.357</v>
       </c>
       <c r="P5">
-        <v>19653248.81501039</v>
+        <v>9953691.026075777</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R5">
-        <v>19653248.81501039</v>
+        <v>26869716.71615482</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
         <v>268</v>
       </c>
       <c r="F6">
-        <v>58.33333333333333</v>
+        <v>86.25</v>
       </c>
       <c r="G6">
-        <v>36.24664166666666</v>
+        <v>53.59324875</v>
       </c>
       <c r="H6">
-        <v>1.11806453685766</v>
+        <v>1.168583693671899</v>
       </c>
       <c r="I6">
-        <v>82.33717331276218</v>
+        <v>111.0447628573425</v>
       </c>
       <c r="J6">
-        <v>8.614673592473483</v>
+        <v>11.61825634377655</v>
       </c>
       <c r="K6">
-        <v>11552.44958097879</v>
+        <v>15580.31412213123</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>8.614673592473483</v>
+        <v>11.61825634377655</v>
       </c>
       <c r="N6">
         <v>0.78</v>
@@ -5426,51 +5420,54 @@
         <v>0.357</v>
       </c>
       <c r="P6">
-        <v>19501316.10176986</v>
+        <v>24218656.64999228</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>19501316.10176986</v>
+        <v>24218656.64999228</v>
       </c>
     </row>
     <row r="7" spans="1:18">
+      <c r="A7">
+        <v>1</v>
+      </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F7">
-        <v>70</v>
+        <v>102.5</v>
       </c>
       <c r="G7">
-        <v>43.49597</v>
+        <v>63.6905275</v>
       </c>
       <c r="H7">
-        <v>1.117102922418433</v>
+        <v>1.16269367240643</v>
       </c>
       <c r="I7">
-        <v>81.4127729405205</v>
+        <v>88.66002137606256</v>
       </c>
       <c r="J7">
-        <v>8.517956555013701</v>
+        <v>9.276212846842</v>
       </c>
       <c r="K7">
-        <v>11422.75009940447</v>
+        <v>12439.58695187206</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>12.5</v>
+        <v>9.276212846842</v>
       </c>
       <c r="N7">
         <v>0.78</v>
@@ -5479,13 +5476,13 @@
         <v>0.357</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>20528170.28621273</v>
       </c>
       <c r="Q7">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>16916025.69007904</v>
+        <v>20528170.28621273</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -5493,40 +5490,40 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E8" t="s">
         <v>268</v>
       </c>
       <c r="F8">
-        <v>81.81818181818181</v>
+        <v>118.75</v>
       </c>
       <c r="G8">
-        <v>50.83944545454546</v>
+        <v>73.78780625</v>
       </c>
       <c r="H8">
-        <v>1.117946837574121</v>
+        <v>1.106353988685262</v>
       </c>
       <c r="I8">
-        <v>81.6824770669085</v>
+        <v>58.92640734562371</v>
       </c>
       <c r="J8">
-        <v>8.546174830209404</v>
+        <v>6.165280453962315</v>
       </c>
       <c r="K8">
-        <v>11460.59137080741</v>
+        <v>8267.764394372543</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>8.546174830209404</v>
+        <v>6.165280453962315</v>
       </c>
       <c r="N8">
         <v>0.78</v>
@@ -5535,13 +5532,13 @@
         <v>0.357</v>
       </c>
       <c r="P8">
-        <v>19395382.82052588</v>
+        <v>15759027.53592782</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>19395382.82052588</v>
+        <v>15759027.53592782</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -5549,10 +5546,10 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="D9" t="s">
         <v>199</v>
@@ -5561,28 +5558,28 @@
         <v>268</v>
       </c>
       <c r="F9">
-        <v>93.63636363636364</v>
+        <v>135</v>
       </c>
       <c r="G9">
-        <v>58.18292090909091</v>
+        <v>83.885085</v>
       </c>
       <c r="H9">
-        <v>1.116999136322191</v>
+        <v>1.105612847460781</v>
       </c>
       <c r="I9">
-        <v>80.77408476341613</v>
+        <v>58.35102979770082</v>
       </c>
       <c r="J9">
-        <v>8.451132665490242</v>
+        <v>6.105080551920921</v>
       </c>
       <c r="K9">
-        <v>11333.13792707572</v>
+        <v>8187.035121736994</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>8.451132665490242</v>
+        <v>6.105080551920921</v>
       </c>
       <c r="N9">
         <v>0.78</v>
@@ -5591,13 +5588,13 @@
         <v>0.357</v>
       </c>
       <c r="P9">
-        <v>19248521.98146494</v>
+        <v>15668235.32712333</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9">
-        <v>19248521.98146494</v>
+        <v>15668235.32712333</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -5605,40 +5602,40 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
         <v>268</v>
       </c>
       <c r="F10">
-        <v>105.4545454545455</v>
+        <v>151.25</v>
       </c>
       <c r="G10">
-        <v>65.52639636363637</v>
+        <v>93.98236375</v>
       </c>
       <c r="H10">
-        <v>1.102371267972709</v>
+        <v>1.104882546049446</v>
       </c>
       <c r="I10">
-        <v>58.73336040657352</v>
+        <v>57.7853660241407</v>
       </c>
       <c r="J10">
-        <v>6.145082573697146</v>
+        <v>6.045896970845131</v>
       </c>
       <c r="K10">
-        <v>8240.678632979347</v>
+        <v>8107.668755842737</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>6.145082573697146</v>
+        <v>6.045896970845131</v>
       </c>
       <c r="N10">
         <v>0.78</v>
@@ -5647,13 +5644,13 @@
         <v>0.357</v>
       </c>
       <c r="P10">
-        <v>15728559.19260539</v>
+        <v>15579031.27558782</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>15728559.19260539</v>
+        <v>15579031.27558782</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -5661,40 +5658,40 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E11" t="s">
         <v>268</v>
       </c>
       <c r="F11">
-        <v>117.2727272727273</v>
+        <v>167.5</v>
       </c>
       <c r="G11">
-        <v>72.86987181818182</v>
+        <v>104.0796425</v>
       </c>
       <c r="H11">
-        <v>1.076056182463523</v>
+        <v>1.104162594802717</v>
       </c>
       <c r="I11">
-        <v>43.6701913632616</v>
+        <v>57.229051138631</v>
       </c>
       <c r="J11">
-        <v>4.569071649889176</v>
+        <v>5.9876915338538</v>
       </c>
       <c r="K11">
-        <v>6127.216463934383</v>
+        <v>8029.614100728623</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>4.569071649889176</v>
+        <v>5.9876915338538</v>
       </c>
       <c r="N11">
         <v>0.78</v>
@@ -5703,13 +5700,13 @@
         <v>0.357</v>
       </c>
       <c r="P11">
-        <v>13370871.01226343</v>
+        <v>15491355.06410149</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>13370871.01226343</v>
+        <v>15491355.06410149</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -5717,40 +5714,40 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E12" t="s">
         <v>268</v>
       </c>
       <c r="F12">
-        <v>129.0909090909091</v>
+        <v>183.75</v>
       </c>
       <c r="G12">
-        <v>80.21334727272728</v>
+        <v>114.17692125</v>
       </c>
       <c r="H12">
-        <v>1.075679233654487</v>
+        <v>1.10345299834357</v>
       </c>
       <c r="I12">
-        <v>43.35713951845845</v>
+        <v>56.68198550890215</v>
       </c>
       <c r="J12">
-        <v>4.536318042350857</v>
+        <v>5.930453816743045</v>
       </c>
       <c r="K12">
-        <v>6083.293221153346</v>
+        <v>7952.857177328758</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>4.536318042350857</v>
+        <v>5.930453816743045</v>
       </c>
       <c r="N12">
         <v>0.78</v>
@@ -5759,54 +5756,51 @@
         <v>0.357</v>
       </c>
       <c r="P12">
-        <v>13322285.00423805</v>
+        <v>15405188.32786324</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>13322285.00423805</v>
+        <v>15405188.32786324</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13">
-        <v>1</v>
-      </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E13" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>140.9090909090909</v>
+        <v>200</v>
       </c>
       <c r="G13">
-        <v>87.55682272727275</v>
+        <v>124.2742</v>
       </c>
       <c r="H13">
-        <v>1.075306010812164</v>
+        <v>1.102753527706858</v>
       </c>
       <c r="I13">
-        <v>43.04772559357354</v>
+        <v>56.14394866790747</v>
       </c>
       <c r="J13">
-        <v>4.503945058671606</v>
+        <v>5.874160752754944</v>
       </c>
       <c r="K13">
-        <v>6039.880402579797</v>
+        <v>7877.367052659434</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>4.503945058671606</v>
+        <v>12.5</v>
       </c>
       <c r="N13">
         <v>0.78</v>
@@ -5815,54 +5809,54 @@
         <v>0.357</v>
       </c>
       <c r="P13">
-        <v>13274280.12597966</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R13">
-        <v>13274280.12597966</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="E14" t="s">
         <v>268</v>
       </c>
       <c r="F14">
-        <v>152.7272727272727</v>
+        <v>225</v>
       </c>
       <c r="G14">
-        <v>94.9002981818182</v>
+        <v>139.808475</v>
       </c>
       <c r="H14">
-        <v>1.074937429258298</v>
+        <v>1.171520579151358</v>
       </c>
       <c r="I14">
-        <v>42.74243741613079</v>
+        <v>91.05103457194322</v>
       </c>
       <c r="J14">
-        <v>4.472003738676076</v>
+        <v>9.526376866434548</v>
       </c>
       <c r="K14">
-        <v>5997.046453639391</v>
+        <v>12775.06190542606</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>4.472003738676076</v>
+        <v>9.526376866434548</v>
       </c>
       <c r="N14">
         <v>0.78</v>
@@ -5871,54 +5865,54 @@
         <v>0.357</v>
       </c>
       <c r="P14">
-        <v>13226931.44501329</v>
+        <v>20918266.91211979</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>13226931.44501329</v>
+        <v>20918266.91211979</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
         <v>268</v>
       </c>
       <c r="F15">
-        <v>164.5454545454546</v>
+        <v>250</v>
       </c>
       <c r="G15">
-        <v>102.2437736363636</v>
+        <v>155.34275</v>
       </c>
       <c r="H15">
-        <v>1.074571723734568</v>
+        <v>1.169479474271847</v>
       </c>
       <c r="I15">
-        <v>42.44025143830053</v>
+        <v>89.59584275363255</v>
       </c>
       <c r="J15">
-        <v>4.440386991847258</v>
+        <v>9.374124827351716</v>
       </c>
       <c r="K15">
-        <v>5954.64776380701</v>
+        <v>12570.8888759752</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>4.440386991847258</v>
+        <v>9.374124827351716</v>
       </c>
       <c r="N15">
         <v>0.78</v>
@@ -5927,54 +5921,54 @@
         <v>0.357</v>
       </c>
       <c r="P15">
-        <v>13180079.64569585</v>
+        <v>20680733.83934183</v>
       </c>
       <c r="Q15">
         <v>0</v>
       </c>
       <c r="R15">
-        <v>13180079.64569585</v>
+        <v>20680733.83934183</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="E16" t="s">
         <v>268</v>
       </c>
       <c r="F16">
-        <v>176.3636363636364</v>
+        <v>275</v>
       </c>
       <c r="G16">
-        <v>109.5872490909091</v>
+        <v>170.877025</v>
       </c>
       <c r="H16">
-        <v>1.074209937926107</v>
+        <v>1.167483607047212</v>
       </c>
       <c r="I16">
-        <v>42.14172995784224</v>
+        <v>88.1783839228849</v>
       </c>
       <c r="J16">
-        <v>4.409153649591002</v>
+        <v>9.225820669383163</v>
       </c>
       <c r="K16">
-        <v>5912.763227174526</v>
+        <v>12372.01003405621</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>4.409153649591002</v>
+        <v>9.225820669383163</v>
       </c>
       <c r="N16">
         <v>0.78</v>
@@ -5983,54 +5977,51 @@
         <v>0.357</v>
       </c>
       <c r="P16">
-        <v>13133811.38246208</v>
+        <v>20449709.24449027</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>13133811.38246208</v>
+        <v>20449709.24449027</v>
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17">
-        <v>1</v>
-      </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D17" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>188.1818181818182</v>
+        <v>300</v>
       </c>
       <c r="G17">
-        <v>116.9307245454546</v>
+        <v>186.4113</v>
       </c>
       <c r="H17">
-        <v>1.07385186693244</v>
+        <v>1.165544304355588</v>
       </c>
       <c r="I17">
-        <v>41.84673069000261</v>
+        <v>86.80361037789667</v>
       </c>
       <c r="J17">
-        <v>4.378288825111254</v>
+        <v>9.08198253555928</v>
       </c>
       <c r="K17">
-        <v>5871.372880250693</v>
+        <v>12179.12021983571</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>4.378288825111254</v>
+        <v>12.5</v>
       </c>
       <c r="N17">
         <v>0.78</v>
@@ -6039,51 +6030,54 @@
         <v>0.357</v>
       </c>
       <c r="P17">
-        <v>13088104.0502434</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R17">
-        <v>13088104.0502434</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="18" spans="1:18">
+      <c r="A18">
+        <v>3</v>
+      </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D18" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="E18" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F18">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="G18">
-        <v>124.2742</v>
+        <v>201.945575</v>
       </c>
       <c r="H18">
-        <v>1.073497749671236</v>
+        <v>1.163647373870699</v>
       </c>
       <c r="I18">
-        <v>41.5553610568925</v>
+        <v>85.46387217707037</v>
       </c>
       <c r="J18">
-        <v>4.34780375763793</v>
+        <v>8.941810037098039</v>
       </c>
       <c r="K18">
-        <v>5830.491795067617</v>
+        <v>11991.14609594921</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>12.5</v>
+        <v>8.941810037098039</v>
       </c>
       <c r="N18">
         <v>0.78</v>
@@ -6092,54 +6086,54 @@
         <v>0.357</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>20008246.50484437</v>
       </c>
       <c r="Q18">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>16916025.69007904</v>
+        <v>20008246.50484437</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" t="s">
         <v>247</v>
-      </c>
-      <c r="D19" t="s">
-        <v>216</v>
       </c>
       <c r="E19" t="s">
         <v>268</v>
       </c>
       <c r="F19">
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="G19">
-        <v>139.808475</v>
+        <v>217.47985</v>
       </c>
       <c r="H19">
-        <v>1.177043298047331</v>
+        <v>1.161802106035698</v>
       </c>
       <c r="I19">
-        <v>96.2123142022311</v>
+        <v>84.16314240620419</v>
       </c>
       <c r="J19">
-        <v>10.06638495203542</v>
+        <v>8.805718865186405</v>
       </c>
       <c r="K19">
-        <v>13499.22354837854</v>
+        <v>11808.64511259227</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>10.06638495203542</v>
+        <v>8.805718865186405</v>
       </c>
       <c r="N19">
         <v>0.78</v>
@@ -6148,54 +6142,54 @@
         <v>0.357</v>
       </c>
       <c r="P19">
-        <v>21763679.27687195</v>
+        <v>19797155.99559797</v>
       </c>
       <c r="Q19">
         <v>0</v>
       </c>
       <c r="R19">
-        <v>21763679.27687195</v>
+        <v>19797155.99559797</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D20" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="E20" t="s">
         <v>268</v>
       </c>
       <c r="F20">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="G20">
-        <v>155.34275</v>
+        <v>233.014125</v>
       </c>
       <c r="H20">
-        <v>1.174803587838369</v>
+        <v>1.15999665002748</v>
       </c>
       <c r="I20">
-        <v>94.54793418988392</v>
+        <v>82.89502726057192</v>
       </c>
       <c r="J20">
-        <v>9.892246225099244</v>
+        <v>8.67304005660262</v>
       </c>
       <c r="K20">
-        <v>13265.70003278259</v>
+        <v>11630.72017670524</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>9.892246225099244</v>
+        <v>8.67304005660262</v>
       </c>
       <c r="N20">
         <v>0.78</v>
@@ -6204,290 +6198,13 @@
         <v>0.357</v>
       </c>
       <c r="P20">
-        <v>21490556.29018191</v>
+        <v>19591637.81303129</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="R20">
-        <v>21490556.29018191</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" t="s">
-        <v>249</v>
-      </c>
-      <c r="D21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E21" t="s">
-        <v>268</v>
-      </c>
-      <c r="F21">
-        <v>275.0000000000001</v>
-      </c>
-      <c r="G21">
-        <v>170.877025</v>
-      </c>
-      <c r="H21">
-        <v>1.172614151122827</v>
-      </c>
-      <c r="I21">
-        <v>92.92567978871516</v>
-      </c>
-      <c r="J21">
-        <v>9.722514965356615</v>
-      </c>
-      <c r="K21">
-        <v>13038.08701884253</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>9.722514965356615</v>
-      </c>
-      <c r="N21">
-        <v>0.78</v>
-      </c>
-      <c r="O21">
-        <v>0.357</v>
-      </c>
-      <c r="P21">
-        <v>21224803.40740003</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>21224803.40740003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="B22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" t="s">
-        <v>250</v>
-      </c>
-      <c r="D22" t="s">
-        <v>222</v>
-      </c>
-      <c r="E22" t="s">
-        <v>255</v>
-      </c>
-      <c r="F22">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G22">
-        <v>186.4113</v>
-      </c>
-      <c r="H22">
-        <v>1.170495072865935</v>
-      </c>
-      <c r="I22">
-        <v>91.35545845273612</v>
-      </c>
-      <c r="J22">
-        <v>9.558227757851759</v>
-      </c>
-      <c r="K22">
-        <v>12817.77458783436</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>12.5</v>
-      </c>
-      <c r="N22">
-        <v>0.78</v>
-      </c>
-      <c r="O22">
-        <v>0.357</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R22">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" t="s">
-        <v>251</v>
-      </c>
-      <c r="D23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E23" t="s">
-        <v>268</v>
-      </c>
-      <c r="F23">
-        <v>325.0000000000001</v>
-      </c>
-      <c r="G23">
-        <v>201.945575</v>
-      </c>
-      <c r="H23">
-        <v>1.168422733861315</v>
-      </c>
-      <c r="I23">
-        <v>89.82431205124385</v>
-      </c>
-      <c r="J23">
-        <v>9.398028835051212</v>
-      </c>
-      <c r="K23">
-        <v>12602.94462838038</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>9.398028835051212</v>
-      </c>
-      <c r="N23">
-        <v>0.78</v>
-      </c>
-      <c r="O23">
-        <v>0.357</v>
-      </c>
-      <c r="P23">
-        <v>20718003.17416135</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>20718003.17416135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" t="s">
-        <v>252</v>
-      </c>
-      <c r="D24" t="s">
-        <v>226</v>
-      </c>
-      <c r="E24" t="s">
-        <v>268</v>
-      </c>
-      <c r="F24">
-        <v>350.0000000000001</v>
-      </c>
-      <c r="G24">
-        <v>217.47985</v>
-      </c>
-      <c r="H24">
-        <v>1.166414577686659</v>
-      </c>
-      <c r="I24">
-        <v>88.34079338086421</v>
-      </c>
-      <c r="J24">
-        <v>9.242813048554448</v>
-      </c>
-      <c r="K24">
-        <v>12394.79715437249</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>9.242813048554448</v>
-      </c>
-      <c r="N24">
-        <v>0.78</v>
-      </c>
-      <c r="O24">
-        <v>0.357</v>
-      </c>
-      <c r="P24">
-        <v>20476162.07385932</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>20476162.07385932</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" t="s">
-        <v>253</v>
-      </c>
-      <c r="D25" t="s">
-        <v>228</v>
-      </c>
-      <c r="E25" t="s">
-        <v>268</v>
-      </c>
-      <c r="F25">
-        <v>375.0000000000001</v>
-      </c>
-      <c r="G25">
-        <v>233.014125</v>
-      </c>
-      <c r="H25">
-        <v>1.164450022888937</v>
-      </c>
-      <c r="I25">
-        <v>86.89361461616916</v>
-      </c>
-      <c r="J25">
-        <v>9.091399389496097</v>
-      </c>
-      <c r="K25">
-        <v>12191.74840930206</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>9.091399389496097</v>
-      </c>
-      <c r="N25">
-        <v>0.78</v>
-      </c>
-      <c r="O25">
-        <v>0.357</v>
-      </c>
-      <c r="P25">
-        <v>20240608.84944247</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>20240608.84944247</v>
+        <v>19591637.81303129</v>
       </c>
     </row>
   </sheetData>
@@ -6497,20 +6214,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="B2">
         <v>4865822.962046022</v>
@@ -6518,143 +6235,143 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="B3">
-        <v>4336559.807486307</v>
+        <v>4271748.703108184</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="B4">
-        <v>4865822.962046022</v>
+        <v>4069304.927154007</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B5">
-        <v>4794198.453627313</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>165</v>
       </c>
       <c r="B6">
-        <v>4340504.755143139</v>
+        <v>4469916.489068738</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="B7">
-        <v>4865822.962046022</v>
+        <v>4078596.630496888</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="B8">
-        <v>4722547.955580813</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="B9">
-        <v>4344391.794437824</v>
+        <v>4656127.234382963</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="B10">
-        <v>4865822.962046022</v>
+        <v>4087662.82751308</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B11">
-        <v>4650847.311906654</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="B12">
-        <v>4348223.961192051</v>
+        <v>4763165.653954888</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B13">
-        <v>4865822.962046022</v>
+        <v>4096513.551423286</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B14">
-        <v>4504622.583510358</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="B15">
-        <v>4352005.453747332</v>
+        <v>4187124.927403578</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B16">
-        <v>4865822.962046022</v>
+        <v>4163863.477126516</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B17">
-        <v>4355751.707740526</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B18">
-        <v>4865822.962046022</v>
+        <v>4216824.582714224</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="B19">
-        <v>4352463.640046223</v>
+        <v>4184956.947409213</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B20">
         <v>4865822.962046022</v>
@@ -6662,23 +6379,23 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B21">
-        <v>4702216.066588552</v>
+        <v>4430711.39240246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>237</v>
+        <v>192</v>
       </c>
       <c r="B22">
-        <v>4356156.422884206</v>
+        <v>4398070.61013838</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B23">
         <v>4865822.962046022</v>
@@ -6686,23 +6403,23 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B24">
-        <v>4535236.113741167</v>
+        <v>4435928.748810861</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="B25">
-        <v>4413960.254057059</v>
+        <v>4401018.831520611</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B26">
         <v>4865822.962046022</v>
@@ -6710,10 +6427,10 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="B27">
-        <v>4521904.191755312</v>
+        <v>4441076.081944307</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -6721,76 +6438,76 @@
         <v>202</v>
       </c>
       <c r="B28">
-        <v>4865822.962046022</v>
+        <v>4403927.801596629</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B29">
-        <v>4854789.212054112</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="B30">
-        <v>4523488.796483492</v>
+        <v>4431436.062867114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B31">
-        <v>4865822.962046022</v>
+        <v>4406799.311033905</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B32">
-        <v>4731939.229730661</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="B33">
-        <v>4525058.832667484</v>
+        <v>4421887.933634564</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B34">
-        <v>4865822.962046022</v>
+        <v>4409633.187231601</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B35">
-        <v>4607039.580147291</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="B36">
-        <v>4526610.414341434</v>
+        <v>4412430.193866032</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B37">
         <v>4865822.962046022</v>
@@ -6798,39 +6515,39 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="B38">
-        <v>4528150.941042197</v>
+        <v>4403061.378298423</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B39">
-        <v>4865822.962046022</v>
+        <v>4153425.085857897</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B40">
-        <v>4807168.102858045</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B41">
-        <v>4529675.988140724</v>
+        <v>4642099.453951705</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B42">
         <v>4865822.962046022</v>
@@ -6838,226 +6555,146 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B43">
-        <v>4671284.311111992</v>
+        <v>4160674.10253235</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="B44">
-        <v>4531186.387882071</v>
+        <v>4412125.875375135</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B45">
-        <v>4865822.962046022</v>
+        <v>4167786.967349901</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B46">
-        <v>4532681.101135243</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="B47">
-        <v>4865822.962046022</v>
+        <v>4646324.312066911</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B48">
-        <v>4391091.449735745</v>
+        <v>4174721.581893245</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B49">
-        <v>4133937.103348901</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B50">
-        <v>4865822.962046022</v>
+        <v>4420809.07446864</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="B51">
-        <v>4636710.743668576</v>
+        <v>4181527.042733391</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B52">
-        <v>4141818.268532108</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="B53">
-        <v>4865822.962046022</v>
+        <v>4650377.760059973</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="B54">
-        <v>4400914.935676467</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B55">
-        <v>4149551.629908944</v>
+        <v>4188168.48133387</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B56">
-        <v>4865822.962046022</v>
+        <v>4429135.882351197</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B57">
-        <v>4641270.4856087</v>
+        <v>4194687.081148683</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B58">
-        <v>4157064.027729862</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="B59">
-        <v>4865822.962046022</v>
+        <v>4654270.613134009</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="B60">
-        <v>4410293.334579322</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>251</v>
-      </c>
-      <c r="B61">
-        <v>4164437.083456788</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>224</v>
-      </c>
-      <c r="B62">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B63">
-        <v>4645631.06209994</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>252</v>
-      </c>
-      <c r="B64">
-        <v>4171606.781266716</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>227</v>
-      </c>
-      <c r="B66">
-        <v>4419256.992265442</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>253</v>
-      </c>
-      <c r="B67">
-        <v>4178644.739062462</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>228</v>
-      </c>
-      <c r="B68">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>229</v>
-      </c>
-      <c r="B69">
-        <v>4649805.566991739</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>254</v>
-      </c>
-      <c r="B70">
-        <v>4185495.351773777</v>
+        <v>4201054.628480863</v>
       </c>
     </row>
   </sheetData>
@@ -7071,37 +6708,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B2">
         <v>8.11266027279845</v>
       </c>
       <c r="C2">
-        <v>8.112660272798408</v>
+        <v>8.112660272797193</v>
       </c>
       <c r="D2">
         <v>141.8178946624533</v>
@@ -7110,21 +6747,21 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520399999994</v>
+        <v>1150.520399999822</v>
       </c>
       <c r="G2">
-        <v>-5.255065873835731E-13</v>
+        <v>-1.550244432781541E-11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B3">
         <v>21.09291642722411</v>
       </c>
       <c r="C3">
-        <v>21.09291642722414</v>
+        <v>21.0929164272241</v>
       </c>
       <c r="D3">
         <v>141.8178946624533</v>
@@ -7133,10 +6770,10 @@
         <v>2991.353</v>
       </c>
       <c r="F3">
-        <v>2991.353000000003</v>
+        <v>2991.352999999998</v>
       </c>
       <c r="G3">
-        <v>1.010589604635734E-13</v>
+        <v>-6.737264030904896E-14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7147,7 +6784,7 @@
         <v>16.2253205455969</v>
       </c>
       <c r="C4">
-        <v>16.22532054559692</v>
+        <v>16.22532054559689</v>
       </c>
       <c r="D4">
         <v>141.8178946624533</v>
@@ -7156,10 +6793,843 @@
         <v>2301.0408</v>
       </c>
       <c r="F4">
-        <v>2301.040800000002</v>
+        <v>2301.040799999999</v>
       </c>
       <c r="G4">
-        <v>8.758443123059551E-14</v>
+        <v>-4.379221561529776E-14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" t="s">
+        <v>293</v>
+      </c>
+      <c r="F7" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" t="s">
+        <v>293</v>
+      </c>
+      <c r="H7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I7" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" t="s">
+        <v>304</v>
+      </c>
+      <c r="I8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F9" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B13" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" t="s">
+        <v>304</v>
+      </c>
+      <c r="E13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" t="s">
+        <v>293</v>
+      </c>
+      <c r="D14" t="s">
+        <v>315</v>
+      </c>
+      <c r="E14" t="s">
+        <v>293</v>
+      </c>
+      <c r="F14" t="s">
+        <v>304</v>
+      </c>
+      <c r="G14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" t="s">
+        <v>293</v>
+      </c>
+      <c r="D15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E16" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" t="s">
+        <v>307</v>
+      </c>
+      <c r="C17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D17" t="s">
+        <v>304</v>
+      </c>
+      <c r="E17" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D20" t="s">
+        <v>322</v>
+      </c>
+      <c r="E20" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" t="s">
+        <v>324</v>
+      </c>
+      <c r="G20" t="s">
+        <v>325</v>
+      </c>
+      <c r="H20" t="s">
+        <v>326</v>
+      </c>
+      <c r="I20" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C21" t="s">
+        <v>293</v>
+      </c>
+      <c r="D21" t="s">
+        <v>322</v>
+      </c>
+      <c r="E21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" t="s">
+        <v>324</v>
+      </c>
+      <c r="G21" t="s">
+        <v>325</v>
+      </c>
+      <c r="H21" t="s">
+        <v>326</v>
+      </c>
+      <c r="I21" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>329</v>
+      </c>
+      <c r="B22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B23" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B26" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>337</v>
+      </c>
+      <c r="B27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>339</v>
+      </c>
+      <c r="B29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B30" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>343</v>
+      </c>
+      <c r="B31" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>345</v>
+      </c>
+      <c r="B32" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>349</v>
+      </c>
+      <c r="B35" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>351</v>
+      </c>
+      <c r="B36" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>353</v>
+      </c>
+      <c r="B37" t="s">
+        <v>354</v>
+      </c>
+      <c r="C37" t="s">
+        <v>284</v>
+      </c>
+      <c r="D37" t="s">
+        <v>355</v>
+      </c>
+      <c r="E37" t="s">
+        <v>323</v>
+      </c>
+      <c r="F37" t="s">
+        <v>356</v>
+      </c>
+      <c r="G37" t="s">
+        <v>288</v>
+      </c>
+      <c r="H37" t="s">
+        <v>357</v>
+      </c>
+      <c r="I37" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>359</v>
+      </c>
+      <c r="B38" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" t="s">
+        <v>360</v>
+      </c>
+      <c r="D38" t="s">
+        <v>355</v>
+      </c>
+      <c r="E38" t="s">
+        <v>323</v>
+      </c>
+      <c r="F38" t="s">
+        <v>356</v>
+      </c>
+      <c r="G38" t="s">
+        <v>288</v>
+      </c>
+      <c r="H38" t="s">
+        <v>357</v>
+      </c>
+      <c r="I38" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>361</v>
+      </c>
+      <c r="B39" t="s">
+        <v>354</v>
+      </c>
+      <c r="C39" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" t="s">
+        <v>355</v>
+      </c>
+      <c r="E39" t="s">
+        <v>323</v>
+      </c>
+      <c r="F39" t="s">
+        <v>356</v>
+      </c>
+      <c r="G39" t="s">
+        <v>288</v>
+      </c>
+      <c r="H39" t="s">
+        <v>357</v>
+      </c>
+      <c r="I39" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>363</v>
+      </c>
+      <c r="B40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C40" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" t="s">
+        <v>355</v>
+      </c>
+      <c r="E40" t="s">
+        <v>323</v>
+      </c>
+      <c r="F40" t="s">
+        <v>356</v>
+      </c>
+      <c r="G40" t="s">
+        <v>288</v>
+      </c>
+      <c r="H40" t="s">
+        <v>357</v>
+      </c>
+      <c r="I40" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>364</v>
+      </c>
+      <c r="B41" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" t="s">
+        <v>365</v>
+      </c>
+      <c r="D41" t="s">
+        <v>355</v>
+      </c>
+      <c r="E41" t="s">
+        <v>323</v>
+      </c>
+      <c r="F41" t="s">
+        <v>356</v>
+      </c>
+      <c r="G41" t="s">
+        <v>288</v>
+      </c>
+      <c r="H41" t="s">
+        <v>357</v>
+      </c>
+      <c r="I41" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C42" t="s">
+        <v>367</v>
+      </c>
+      <c r="D42" t="s">
+        <v>355</v>
+      </c>
+      <c r="E42" t="s">
+        <v>323</v>
+      </c>
+      <c r="F42" t="s">
+        <v>356</v>
+      </c>
+      <c r="G42" t="s">
+        <v>288</v>
+      </c>
+      <c r="H42" t="s">
+        <v>357</v>
+      </c>
+      <c r="I42" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>368</v>
+      </c>
+      <c r="B43" t="s">
+        <v>354</v>
+      </c>
+      <c r="C43" t="s">
+        <v>293</v>
+      </c>
+      <c r="D43" t="s">
+        <v>355</v>
+      </c>
+      <c r="E43" t="s">
+        <v>323</v>
+      </c>
+      <c r="F43" t="s">
+        <v>356</v>
+      </c>
+      <c r="G43" t="s">
+        <v>288</v>
+      </c>
+      <c r="H43" t="s">
+        <v>357</v>
+      </c>
+      <c r="I43" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" t="s">
+        <v>284</v>
+      </c>
+      <c r="D44" t="s">
+        <v>355</v>
+      </c>
+      <c r="E44" t="s">
+        <v>323</v>
+      </c>
+      <c r="F44" t="s">
+        <v>356</v>
+      </c>
+      <c r="G44" t="s">
+        <v>288</v>
+      </c>
+      <c r="H44" t="s">
+        <v>357</v>
+      </c>
+      <c r="I44" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>369</v>
+      </c>
+      <c r="B45" t="s">
+        <v>354</v>
+      </c>
+      <c r="C45" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" t="s">
+        <v>355</v>
+      </c>
+      <c r="E45" t="s">
+        <v>323</v>
+      </c>
+      <c r="F45" t="s">
+        <v>356</v>
+      </c>
+      <c r="G45" t="s">
+        <v>288</v>
+      </c>
+      <c r="H45" t="s">
+        <v>357</v>
+      </c>
+      <c r="I45" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>370</v>
+      </c>
+      <c r="B46" t="s">
+        <v>354</v>
+      </c>
+      <c r="C46" t="s">
+        <v>371</v>
+      </c>
+      <c r="D46" t="s">
+        <v>372</v>
+      </c>
+      <c r="E46" t="s">
+        <v>373</v>
+      </c>
+      <c r="F46" t="s">
+        <v>304</v>
+      </c>
+      <c r="G46" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>374</v>
+      </c>
+      <c r="B47" t="s">
+        <v>354</v>
+      </c>
+      <c r="C47" t="s">
+        <v>342</v>
+      </c>
+      <c r="D47" t="s">
+        <v>372</v>
+      </c>
+      <c r="E47" t="s">
+        <v>293</v>
+      </c>
+      <c r="F47" t="s">
+        <v>304</v>
+      </c>
+      <c r="G47" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>375</v>
+      </c>
+      <c r="B48" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" t="s">
+        <v>342</v>
+      </c>
+      <c r="D48" t="s">
+        <v>372</v>
+      </c>
+      <c r="E48" t="s">
+        <v>293</v>
+      </c>
+      <c r="F48" t="s">
+        <v>304</v>
+      </c>
+      <c r="G48" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>376</v>
+      </c>
+      <c r="B49" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49" t="s">
+        <v>372</v>
+      </c>
+      <c r="E49" t="s">
+        <v>293</v>
+      </c>
+      <c r="F49" t="s">
+        <v>304</v>
+      </c>
+      <c r="G49" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>377</v>
+      </c>
+      <c r="B50" t="s">
+        <v>354</v>
+      </c>
+      <c r="C50" t="s">
+        <v>378</v>
+      </c>
+      <c r="D50" t="s">
+        <v>304</v>
+      </c>
+      <c r="E50" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
